--- a/task6/posts.xlsx
+++ b/task6/posts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\School\6_GT-OMSCS\3_F25\6747_AMRE\2025_NSA-CBC\task6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\devel\nsa-cbc-2025\task6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3607C4-D211-49A4-8BC5-7026CB45386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ECC391-3B5B-43C1-9A0D-D5EAC7D3225F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E4E6333-201C-45A3-B1EA-2C0BDE49BD14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3E4E6333-201C-45A3-B1EA-2C0BDE49BD14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1181,18 +1181,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF06D2D9-1109-4F81-B613-6BAFEBBA2617}">
   <dimension ref="A1:H122"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" customWidth="1"/>
-    <col min="6" max="6" width="159.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" customWidth="1"/>
+    <col min="6" max="6" width="159.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>241</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>236</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>238</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>239</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>234</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>235</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>191</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>194</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>209</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>211</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>215</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>202</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>207</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>228</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>186</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>188</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>190</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>230</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>183</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>155</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>157</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>161</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>163</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>165</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>167</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>169</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>171</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>173</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>175</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>177</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>179</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>219</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>44</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>21</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>226</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>227</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>204</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>208</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>212</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>231</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>232</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>59</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>223</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>195</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>200</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>225</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>98</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>100</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>104</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>109</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>111</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>113</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>115</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>117</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>65</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>93</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>77</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>123</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>125</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>129</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>131</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>79</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>82</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>133</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>141</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>143</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>69</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>145</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>147</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>149</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>151</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>153</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>213</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>217</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>218</v>
       </c>
